--- a/data/46267X10_-_AllReports.xlsx
+++ b/data/46267X10_-_AllReports.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income Statement" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance Sheet" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flow" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ratio Analysis" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Income Statement" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Balance Sheet" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Cash Flow" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Ratio Analysis" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -789,7 +789,7 @@
         </is>
       </c>
       <c r="B21" s="4" t="n">
-        <v>-29.5</v>
+        <v>-29.178</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>104.675</v>
@@ -1312,7 +1312,7 @@
         </is>
       </c>
       <c r="B21" s="4" t="n">
-        <v>6674.834</v>
+        <v>6675.401</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>6269.12</v>
@@ -1526,7 +1526,7 @@
         </is>
       </c>
       <c r="B35" s="4" t="n">
-        <v>4770.757</v>
+        <v>4772.249</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>4438.077</v>
